--- a/examples/results/Tryptophan_design_results_ecFactory_level_1_result.xlsx
+++ b/examples/results/Tryptophan_design_results_ecFactory_level_1_result.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>gene_name</t>
@@ -466,7 +471,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>b4467</t>
         </is>
@@ -487,14 +492,14 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-9.908976254592349e-17</v>
+        <v>-2.179974776010317e-15</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>b4468</t>
         </is>
@@ -515,14 +520,14 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4.503629712599597e-14</v>
+        <v>2.770549763790643e-13</v>
       </c>
       <c r="H3" t="n">
-        <v>-9.115036088105764e-05</v>
+        <v>-9.313539209499633e-05</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>b2979</t>
         </is>
@@ -543,14 +548,14 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3.616776336851162e-15</v>
+        <v>2.814149259358164e-14</v>
       </c>
       <c r="H4" t="n">
-        <v>-9.115036097964629e-05</v>
+        <v>-9.313539254815938e-05</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>b3916</t>
         </is>
@@ -573,42 +578,42 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>b4025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1000</v>
+        <v>0.1824571256088911</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OE</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>3.82486483842342e-14</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>b2925</t>
         </is>
@@ -631,14 +636,14 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>b2097</t>
         </is>
@@ -659,14 +664,14 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>b2296</t>
         </is>
@@ -687,14 +692,14 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.585436202455304e-15</v>
+        <v>-3.567231455524434e-15</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>b3115</t>
         </is>
@@ -717,14 +722,14 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>b2297</t>
         </is>
@@ -747,14 +752,14 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>b3709</t>
         </is>
@@ -780,7 +785,7 @@
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>b3161</t>
         </is>
@@ -806,7 +811,7 @@
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>b0112</t>
         </is>
@@ -832,7 +837,7 @@
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>b1723</t>
         </is>
@@ -853,14 +858,14 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2.108828328790861e-12</v>
+        <v>8.736744373155259e-12</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>b3708</t>
         </is>
@@ -881,14 +886,14 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.034497122102086e-13</v>
+        <v>3.805046885892729e-14</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>b1264</t>
         </is>
@@ -909,14 +914,14 @@
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>b1260</t>
         </is>
@@ -937,14 +942,14 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.05658377824727687</v>
+        <v>-0.05649804552444944</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>b1262</t>
         </is>
@@ -965,14 +970,14 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>b1263</t>
         </is>
@@ -993,14 +998,14 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.25</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>b1261</t>
         </is>
@@ -1021,14 +1026,14 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.05658368941756006</v>
+        <v>-0.05659603213146488</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>b1693</t>
         </is>
@@ -1049,14 +1054,14 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.25</v>
+        <v>1.248531009433552e-14</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>b3389</t>
         </is>
@@ -1077,14 +1082,14 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.25</v>
+        <v>9.908976265345648e-16</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>b2329</t>
         </is>
@@ -1105,14 +1110,14 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.25</v>
+        <v>-1.98179525306913e-16</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.25</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>b1704</t>
         </is>
@@ -1135,14 +1140,14 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>b0908</t>
         </is>
@@ -1163,14 +1168,14 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.086646106655169e-14</v>
+        <v>3.491923235907807e-12</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>b3281</t>
         </is>
@@ -1191,14 +1196,14 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.437792456101654e-13</v>
+        <v>1.961977300538439e-14</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.002456747357808343</v>
+        <v>0.00246637325015703</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>b0754</t>
         </is>
@@ -1219,14 +1224,14 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.25</v>
+        <v>-5.94538575920739e-16</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>b3390</t>
         </is>
@@ -1249,14 +1254,14 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>b0388</t>
         </is>
@@ -1277,14 +1282,14 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.25</v>
+        <v>8.323540062890345e-15</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>b2601</t>
         </is>
@@ -1307,14 +1312,14 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>b4094</t>
         </is>
@@ -1335,14 +1340,14 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-5.449936945940107e-16</v>
+        <v>2.885493888468653e-13</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1964705108954162</v>
+        <v>0.196798132308395</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>b4383</t>
         </is>
@@ -1363,14 +1368,14 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>4.954488132672824e-17</v>
+        <v>1.98179525306913e-16</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.01221514615465938</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>b3870</t>
         </is>
@@ -1391,14 +1396,14 @@
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>-4.753335914486308e-13</v>
+        <v>1.330379153385307e-12</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>b2417</t>
         </is>
@@ -1419,14 +1424,14 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.09873563999123627</v>
+        <v>-0.3949425599649451</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2418714099521334</v>
+        <v>-0.9674856398085334</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>b1817</t>
         </is>
@@ -1449,14 +1454,14 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>b1621</t>
         </is>
@@ -1479,14 +1484,14 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>b1818</t>
         </is>
@@ -1509,14 +1514,14 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>b1819</t>
         </is>
@@ -1539,14 +1544,14 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>b1101</t>
         </is>
@@ -1567,14 +1572,14 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.07528620790610717</v>
+        <v>-0.3011448316241171</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.244305074792047</v>
+        <v>-0.9772202991682226</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>b4226</t>
         </is>
@@ -1597,14 +1602,14 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>b2744</t>
         </is>
@@ -1625,14 +1630,14 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>6.624150633383566e-14</v>
+        <v>4.597764987120381e-14</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.004508877205350624</v>
+        <v>-0.004518503097356697</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>b2502</t>
         </is>
@@ -1655,14 +1660,14 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>b0728</t>
         </is>
@@ -1683,14 +1688,14 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>4.409494438078813e-15</v>
+        <v>1.98179525306913e-16</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.04558452623620536</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>b0729</t>
         </is>
@@ -1711,14 +1716,14 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>8.34831250355371e-14</v>
+        <v>1.028551736342878e-13</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.04558452623632846</v>
+        <v>-0.04581675721038668</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>b3919</t>
         </is>
@@ -1739,14 +1744,14 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>5.459845922205453e-14</v>
+        <v>2.158175030592282e-13</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.005302093262610551</v>
+        <v>-0.005311719155056809</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>b0451</t>
         </is>
@@ -1772,7 +1777,7 @@
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>b0875</t>
         </is>
@@ -1798,7 +1803,7 @@
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>b3875</t>
         </is>
@@ -1824,7 +1829,7 @@
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>b1319</t>
         </is>
@@ -1850,7 +1855,7 @@
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>b0957</t>
         </is>
@@ -1876,7 +1881,7 @@
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>b2551</t>
         </is>
@@ -1897,14 +1902,14 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>-6.341744809821215e-15</v>
+        <v>2.001613205599821e-14</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>b0529</t>
         </is>
@@ -1925,14 +1930,14 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>-8.948796465233656e-13</v>
+        <v>1.240603828421275e-13</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>b1852</t>
         </is>
@@ -1953,14 +1958,14 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>5.202212539306466e-15</v>
+        <v>-7.927181012276519e-16</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>b0767</t>
         </is>
@@ -1981,42 +1986,42 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.2500000000000001</v>
+        <v>8.820970671410697e-13</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>b2029</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>0.1824571256088911</v>
+        <v>1000</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>OE</t>
         </is>
       </c>
       <c r="E56" t="n">
         <v>2</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.2438761579269342</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>b0008</t>
         </is>
@@ -2039,14 +2044,14 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>4.77117207176393e-14</v>
+        <v>1.9580137100323e-13</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.2313414272383159</v>
+        <v>-0.2316690486513085</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>b2464</t>
         </is>
@@ -2069,14 +2074,14 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>b2906</t>
         </is>
@@ -2097,14 +2102,14 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.7498940131581511</v>
+        <v>0.9999999999999957</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>b3867</t>
         </is>
@@ -2125,14 +2130,14 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>3.765410980831347e-15</v>
+        <v>-1.98179525306913e-16</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>b3125</t>
         </is>
@@ -2153,14 +2158,14 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>-2.93702056504845e-13</v>
+        <v>-1.298868608861508e-12</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>b1033</t>
         </is>
@@ -2181,14 +2186,14 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>b0508</t>
         </is>
@@ -2209,14 +2214,14 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>9.215347926771453e-15</v>
+        <v>-3.408687835278903e-14</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>b0509</t>
         </is>
@@ -2237,14 +2242,14 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>b3553</t>
         </is>
@@ -2265,14 +2270,14 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>8.120406049450759e-14</v>
+        <v>1.288166914494934e-14</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.25</v>
+        <v>-0.05034215391138917</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>b1199</t>
         </is>
@@ -2293,14 +2298,14 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>4.984215061468861e-14</v>
+        <v>1.93938483465345e-12</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.1160803467940846</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>b1200</t>
         </is>
@@ -2321,14 +2326,14 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>3.864500743484803e-15</v>
+        <v>3.96359050613826e-16</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.1160803467939918</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>b3946</t>
         </is>
@@ -2349,14 +2354,14 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>b1198</t>
         </is>
@@ -2377,14 +2382,14 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>-1.506164392332539e-14</v>
+        <v>1.583454407202235e-13</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.1160803467940041</v>
+        <v>-0.04187215185690053</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>b0825</t>
         </is>
@@ -2405,14 +2410,14 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>8.224945749050156e-13</v>
+        <v>3.099725955325426e-12</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>b1473</t>
         </is>
